--- a/excel_files/8.10.1.xlsx
+++ b/excel_files/8.10.1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10935"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -574,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -584,7 +584,7 @@
     <col min="12" max="12" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="10" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="10" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>13</v>
       </c>
@@ -595,8 +595,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -657,8 +657,11 @@
       <c r="T3" s="4">
         <v>2023</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U3" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>14</v>
       </c>
@@ -719,8 +722,12 @@
       <c r="T4" s="8">
         <v>6.7904451646088795</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="24" x14ac:dyDescent="0.25">
+      <c r="U4" s="8">
+        <f t="shared" ref="U4" si="0">U6/U8*100000</f>
+        <v>6.2985169685983706</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="24" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
@@ -781,8 +788,12 @@
       <c r="T5" s="8">
         <v>47.957518975050206</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U5" s="8">
+        <f t="shared" ref="U5" si="1">U7/U8*100000</f>
+        <v>52.397859913109471</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>17</v>
       </c>
@@ -843,8 +854,11 @@
       <c r="T6" s="17">
         <v>320</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U6" s="17">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>16</v>
       </c>
@@ -905,8 +919,11 @@
       <c r="T7" s="17">
         <v>2260</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U7" s="17">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>23</v>
       </c>
@@ -967,8 +984,11 @@
       <c r="T8" s="9">
         <v>4712504</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U8" s="9">
+        <v>4826533</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>12</v>
       </c>
@@ -990,7 +1010,7 @@
       <c r="M9" s="6"/>
       <c r="N9" s="11"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -1006,7 +1026,7 @@
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1023,7 +1043,7 @@
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1039,7 +1059,7 @@
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1055,7 +1075,7 @@
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1071,7 +1091,7 @@
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1087,7 +1107,7 @@
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
